--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:04:23+00:00</t>
+    <t>2026-10-15T15:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,7 +283,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-sp-subject-sourcePatientInfo-ins:Lorsque subject.identifier porte un matricule INS et que context.sourcePatientInfo est fourni, la ressource Patient contenue référencée par context.sourcePatientInfo doit porter le même matricule INS (même system et même value). {(subject.identifier.where(system in ('urn:oid:1.2.250.1.213.1.4.8' | 'urn:oid:1.2.250.1.213.1.4.9' | 'urn:oid:1.2.250.1.213.1.4.10' | 'urn:oid:1.2.250.1.213.1.4.11')).exists() and context.sourcePatientInfo.exists()) implies contained.ofType(Patient).where(('#' + id) = %resource.context.sourcePatientInfo.reference).identifier.where(system = %resource.subject.identifier.system and value = %resource.subject.identifier.value).exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -861,7 +861,7 @@
 </t>
   </si>
   <si>
-    <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
+    <t>Patient titulaire du dossier dans le système cible. Lorsque le patient dispose d'une identité INS qualifiée, le matricule INS est porté par subject.identifier (référence logique, admise par IHE MHD ITI-105 §2:3.105.4.1.2.2 pour un identifiant national). La référence peut aussi pointer une ressource Patient déjà connue du système cible. Conformément à IHE MHD, la ressource Patient n'est pas contenue (contained) : les traits du patient tels que connus du producteur sont portés par context.sourcePatientInfo. Lorsque context.sourcePatientInfo est fourni, son matricule INS doit être identique à celui de subject.identifier (invariant constr-sp-subject-sourcePatientInfo-ins) ; en cas de discordance, la transaction est rejetée.</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -1635,10 +1635,6 @@
   </si>
   <si>
     <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), cf spécifications IHE MHD ITI-105 §2:3.105.4.1.2.2. {reference.exists() implies reference.startsWith('#')}</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>
@@ -9744,7 +9740,7 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>514</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9765,15 +9761,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9796,16 +9792,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9855,7 +9851,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9873,22 +9869,22 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
   </sheetData>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:21:59+00:00</t>
+    <t>2026-10-15T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1158,7 +1158,11 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J08-XdsConfidentialityCode-CISIS/FHIR/JDV-J08-XdsConfidentialityCode-CISIS</t>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (U, L, M, N, R, V) du statut de visibilité (MASQUE_PS, INVISIBLE_PATIENT, etc...) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1174,6 +1178,30 @@
   </si>
   <si>
     <t>DocumentEntry.confidentialityCode</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality</t>
+  </si>
+  <si>
+    <t>confidentiality</t>
+  </si>
+  <si>
+    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint, ...). En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-Confidentiality</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus</t>
+  </si>
+  <si>
+    <t>visibilityStatus</t>
+  </si>
+  <si>
+    <t>Statut de visibilité du document (invisible patient, invisible représentants légaux, masqué PS, etc...).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -1982,12 +2010,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ64"/>
+  <dimension ref="A1:AQ66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.37890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2013,7 +2041,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="255.0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -6453,7 +6481,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>358</v>
       </c>
@@ -6466,7 +6494,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>82</v>
@@ -6520,24 +6548,26 @@
       <c r="X37" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y37" s="2"/>
+      <c r="Y37" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="Z37" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>358</v>
@@ -6558,32 +6588,34 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6604,16 +6636,20 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>316</v>
+        <v>242</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6637,13 +6673,11 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6661,10 +6695,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>82</v>
@@ -6679,32 +6713,34 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6713,28 +6749,32 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6758,13 +6798,11 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6782,81 +6820,79 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>111</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>379</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6905,10 +6941,10 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
@@ -6917,16 +6953,16 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>381</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6943,46 +6979,42 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7030,19 +7062,19 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7051,7 +7083,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7068,21 +7100,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7091,18 +7123,20 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>378</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>379</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7151,40 +7185,40 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>377</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7196,35 +7230,39 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7272,19 +7310,19 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7293,7 +7331,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7317,14 +7355,14 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7333,20 +7371,18 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7383,60 +7419,60 @@
         <v>80</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>391</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7444,7 +7480,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
@@ -7456,21 +7492,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>109</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7482,7 +7516,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>391</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7494,13 +7528,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>393</v>
+        <v>80</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7518,7 +7552,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7530,7 +7564,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7539,61 +7573,61 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7605,7 +7639,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7617,43 +7651,43 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7662,7 +7696,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>403</v>
+        <v>111</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7679,10 +7713,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7702,22 +7736,20 @@
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>405</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7730,7 +7762,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7742,13 +7774,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7766,7 +7798,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7787,7 +7819,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7796,18 +7828,18 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7818,10 +7850,10 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -7830,19 +7862,17 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>414</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7855,7 +7885,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7867,13 +7897,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7891,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7912,7 +7942,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7921,7 +7951,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7929,10 +7959,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7940,7 +7970,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -7952,22 +7982,22 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8016,7 +8046,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8037,7 +8067,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8046,7 +8076,7 @@
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
@@ -8054,10 +8084,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8068,7 +8098,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -8080,19 +8110,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8105,7 +8135,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>80</v>
@@ -8141,7 +8171,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8162,7 +8192,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8171,7 +8201,7 @@
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>80</v>
@@ -8179,10 +8209,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8190,7 +8220,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8205,17 +8235,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>433</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8228,7 +8260,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8264,7 +8296,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8285,7 +8317,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8300,12 +8332,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8319,7 +8351,7 @@
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8328,17 +8360,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8387,7 +8421,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8408,7 +8442,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8423,12 +8457,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8436,13 +8470,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
@@ -8451,18 +8485,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8474,7 +8508,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8486,11 +8520,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8508,7 +8544,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8520,19 +8556,19 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>456</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>373</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>458</v>
+        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8541,15 +8577,15 @@
         <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>459</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8572,18 +8608,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>316</v>
+        <v>455</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8631,7 +8667,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8652,7 +8688,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8667,12 +8703,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8686,24 +8722,26 @@
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>108</v>
+        <v>461</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8728,13 +8766,11 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8752,7 +8788,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8764,19 +8800,19 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8785,47 +8821,47 @@
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>115</v>
+        <v>470</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>116</v>
+        <v>471</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>117</v>
+        <v>472</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8875,19 +8911,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>121</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8896,7 +8932,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>111</v>
+        <v>473</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8913,46 +8949,42 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -9000,19 +9032,19 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9021,7 +9053,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9038,14 +9070,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9064,15 +9096,17 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>469</v>
+        <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>115</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9121,7 +9155,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9133,22 +9167,22 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>474</v>
+        <v>111</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9166,37 +9200,39 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>328</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>329</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9220,13 +9256,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>481</v>
+        <v>80</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9244,7 +9280,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>331</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9256,16 +9292,16 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>482</v>
+        <v>122</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>484</v>
+        <v>192</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9277,15 +9313,15 @@
         <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9296,25 +9332,25 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9365,13 +9401,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9380,33 +9416,33 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>493</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9420,7 +9456,7 @@
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -9432,12 +9468,14 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9462,11 +9500,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9484,48 +9524,48 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9545,23 +9585,19 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>242</v>
+        <v>496</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9585,11 +9621,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9607,7 +9645,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9619,7 +9657,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>498</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9631,7 +9669,7 @@
         <v>500</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9640,15 +9678,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9671,13 +9709,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>511</v>
+        <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9704,13 +9742,11 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>80</v>
+        <v>506</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9728,7 +9764,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9740,19 +9776,19 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>507</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>271</v>
+        <v>508</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>272</v>
+        <v>509</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>273</v>
+        <v>510</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9761,15 +9797,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9780,10 +9816,10 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -9792,18 +9828,20 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9827,13 +9865,11 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>80</v>
+        <v>517</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9851,44 +9887,288 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>523</v>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>532</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ64">
+  <autoFilter ref="A1:AQ66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9898,7 +10178,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
